--- a/workshop/ac3898db99.xlsx
+++ b/workshop/ac3898db99.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="素材清单（人工去挑）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -2433,161 +2433,417 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="44" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>层级</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>场景</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>检索词（英文，主用）</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>建议条数</t>
-        </is>
-      </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
-          <t>来源</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="8" t="inlineStr">
+          <t>覆盖镜次</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>怎么做（检索词 / 拍摄内容）</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>去哪找</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>要几条</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>L1 自拍</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>片头钩子 · 自拍空镜</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>001-002</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>手机拍：园区大门 / 拉闸门 / 车间过道横移 / 账本红字，每条 5-8 秒</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>自己拍（手机横屏）</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>这 3 秒决定完播。素材站的画面「没有你的厂味」，钩子必用自拍</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr"/>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>厂房外景</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>005、009、013、017、021、025、029、033</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="7" t="inlineStr"/>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>车间内景</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>006、010、014、018、022、026、030、034</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>empty factory / idle production line</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>仓库</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>003、007、011、015、019、023、027、031</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>empty warehouse / cleared shelves</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>L2 免费站</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>货车物流</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>004、008、012、016、020、024、028、032</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>empty loading dock / idle truck</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>Pexels / Pixabay（免署名、可商用）</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>L1 自制</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>数据图表 · Excel 出图（叠加层）</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>005-006、009-011、029、034</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>用国家统计局 / 地方统计局 / 海关总署的官方数据，自己用 Excel 出图</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>自己做（Excel 截图或导出 PNG 透明底）</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>这是叠加在场景素材上的透明图，不占镜次、不替代空镜。带数字的镜头一律上自己出的图——这是可信度来源，也是素材站给不了的</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>L1 自拍</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>片尾落点 · 自拍空镜</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>035-036</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>手机拍：厂区远景 / 关门镜头 / 老板背影 / 空账本合上</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>自己拍</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>2-3</t>
         </is>
       </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="26" customHeight="1">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>车间内景</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>empty factory / idle production line</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="26" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>仓库</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>empty warehouse / cleared shelves</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="26" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>货车物流</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>empty loading dock / idle truck</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>2-3</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Pexels / Pixabay（免署名可商用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Pexels/Pixabay 免署名可商用（注意顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账。</t>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>收尾要留白，自拍空镜最压得住；接避坑清单上屏</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="7" t="inlineStr"/>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>L3 AI 兜底</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>仅在实拍和素材站都拿不到时启用</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>可灵 / 即梦 / Runway；或 Pexels、Pixabay 的 AI 素材专区</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>按需</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>AI 视频细节仍有破绽，一眼假。除非「货堆到天花板」这种实拍拍不到的，否则别用</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>用法：从左往右办——『去哪找』决定打开哪个站还是拿手机；办完一行就在「✓」列打个勾。浅蓝底 = 要你自己拍/自己出图（L1），这最容易拖着不做，先办。Pexels/Pixabay 免署名可商用（注意结果顶部「赞助」行是 iStock 付费位）；Videvo 逐条协议不同需逐条看；央视/央视频/他人成片一律别用。下载后按「问题类型_场景_序号.mp4」命名，并记入素材台账（另一张表）。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A11:I11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/workshop/ac3898db99.xlsx
+++ b/workshop/ac3898db99.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="剪辑底稿" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材采集单（照着办）" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="节奏与声音标准" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：77.5 秒　镜次：36</t>
+          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：84.8 秒　镜次：37</t>
         </is>
       </c>
     </row>
@@ -595,14 +595,14 @@
         <v>0</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>说关就关</t>
+          <t>江苏一家五金机械厂</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
@@ -644,96 +644,104 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>1984万</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>快切/冲突</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>空镜快切</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>【待挑】倒闭关停_车间内景_002　搜：empty factory / idle production line</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>数字上大字幕：1984万</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>快切提示音</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>开场悬念</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>硬切</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>钱到底卡在哪</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>钱到底</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>快切/冲突</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>空镜快切</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_车间内景_002　搜：empty factory / idle production line</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>【待挑】倒闭关停_仓库_003　搜：empty warehouse / cleared shelves</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr"/>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>重音咚 / 唰</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>开场悬念</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>硬切</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>003</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>江苏一家五金机械厂</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>推进</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>空镜</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_仓库_003　搜：empty warehouse / cleared shelves</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr"/>
-      <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>开场悬念</t>
-        </is>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>叠化</t>
         </is>
       </c>
     </row>
@@ -744,17 +752,17 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>公开报道里的关键数字</t>
+          <t>江苏一家五金机械厂</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -792,17 +800,17 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>1984万</t>
+          <t>栽在「倒闭 / 关停」上</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -820,16 +828,8 @@
           <t>【待挑】倒闭关停_厂房外景_005　搜：abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>数字上大字幕：1984万</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>数字叮</t>
-        </is>
-      </c>
+      <c r="I9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
       <c r="K9" s="7" t="inlineStr">
         <is>
           <t>开场悬念</t>
@@ -848,27 +848,27 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>1.21亿</t>
+          <t>先把事实摆出来</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>推进</t>
+          <t>陈述/数字重音</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>空镜</t>
+          <t>图表+实拍</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
@@ -876,24 +876,16 @@
           <t>【待挑】倒闭关停_车间内景_006　搜：empty factory / idle production line</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>数字上大字幕：1.21亿</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr">
-        <is>
-          <t>数字叮</t>
-        </is>
-      </c>
+      <c r="I10" s="8" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
       <c r="K10" s="7" t="inlineStr">
         <is>
-          <t>开场悬念</t>
+          <t>中段推进</t>
         </is>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
-          <t>叠化</t>
+          <t>硬切</t>
         </is>
       </c>
     </row>
@@ -904,17 +896,17 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>10.1</v>
+        <v>13.2</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>先把事实说清楚</t>
+          <t>溧阳迅隆科技及关联精密机械公司实质合并破产清算</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -952,17 +944,17 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>10.1</v>
+        <v>13.2</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>溧阳迅隆科技及关联精密机械公司实质合并破产清算</t>
+          <t>2026年9月宣告破产</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -980,8 +972,16 @@
           <t>【待挑】倒闭关停_货车物流_008　搜：empty loading dock / idle truck</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr"/>
-      <c r="J12" s="7" t="inlineStr"/>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>数字上大字幕：2026年</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>数字叮</t>
+        </is>
+      </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -1000,17 +1000,17 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2026年9月宣告破产</t>
+          <t>资产总额1984万</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>数字上大字幕：2026年</t>
+          <t>数字上大字幕：1984万</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
@@ -1056,17 +1056,17 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>15.8</v>
+        <v>17.4</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>17.7</v>
+        <v>19.3</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>1.9</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>资产总额1984万</t>
+          <t>债务总额1.21亿</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I14" s="8" t="inlineStr">
         <is>
-          <t>数字上大字幕：1984万</t>
+          <t>数字上大字幕：1.21亿</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
@@ -1112,17 +1112,17 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>17.7</v>
+        <v>19.3</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>19.6</v>
+        <v>21</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>债务总额1.21亿</t>
+          <t>早已停止生产经营</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1140,16 +1140,8 @@
           <t>【待挑】倒闭关停_仓库_011　搜：empty warehouse / cleared shelves</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>数字上大字幕：1.21亿</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>数字叮</t>
-        </is>
-      </c>
+      <c r="I15" s="8" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
       <c r="K15" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -1168,17 +1160,17 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>19.6</v>
+        <v>21</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>1.7</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>早已停止生产经营</t>
+          <t>公开信息里的数字</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1216,27 +1208,27 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>21.3</v>
+        <v>22.7</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>23.1</v>
+        <v>25</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>打个比方</t>
+          <t>1984万，1.21亿</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>陈述/数字重音</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>图表+实拍</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1244,8 +1236,16 @@
           <t>【待挑】倒闭关停_厂房外景_013　搜：abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr"/>
-      <c r="J17" s="7" t="inlineStr"/>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>数字上大字幕：1984万，1.21亿</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>数字叮</t>
+        </is>
+      </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -1264,17 +1264,17 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>23.1</v>
+        <v>25</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>24.9</v>
+        <v>26.8</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>1.8</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>厂子就是一口锅</t>
+          <t>打个比方</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1312,17 +1312,17 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>24.9</v>
+        <v>26.8</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>27.4</v>
+        <v>28.6</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>订单是火，现金是锅里的水</t>
+          <t>厂子就是一口锅</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1360,17 +1360,17 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>27.4</v>
+        <v>28.6</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>29.3</v>
+        <v>31.1</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>火一停，水凉得飞快</t>
+          <t>订单是火，现金是锅里的水</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1408,27 +1408,27 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>29.3</v>
+        <v>31.1</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>31.1</v>
+        <v>33</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>①战略视角</t>
+          <t>火一停，水凉得飞快</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>转折/停顿</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>素材(比喻画面)</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1436,11 +1436,7 @@
           <t>【待挑】倒闭关停_厂房外景_017　搜：abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：战略视角</t>
-        </is>
-      </c>
+      <c r="I21" s="8" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr"/>
       <c r="K21" s="7" t="inlineStr">
         <is>
@@ -1460,17 +1456,17 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>31.1</v>
+        <v>33</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>32.9</v>
+        <v>35.1</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>是否死守低端红海</t>
+          <t>本案的财务病灶很具体</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1508,17 +1504,17 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>32.9</v>
+        <v>35.1</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>35.6</v>
+        <v>37.2</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>无产品壁垒，靠低价内卷抢单</t>
+          <t>关联公司实质合并破产</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1556,17 +1552,17 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>35.6</v>
+        <v>37.2</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>37.4</v>
+        <v>39.9</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>②财务视角</t>
+          <t>早已停止经营，无人申请重整</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1584,11 +1580,7 @@
           <t>【待挑】倒闭关停_货车物流_020　搜：empty loading dock / idle truck</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：财务视角</t>
-        </is>
-      </c>
+      <c r="I24" s="8" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr"/>
       <c r="K24" s="7" t="inlineStr">
         <is>
@@ -1608,17 +1600,17 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>37.4</v>
+        <v>39.9</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>39.2</v>
+        <v>41.7</v>
       </c>
       <c r="D25" s="7" t="n">
         <v>1.8</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>现金流是否断裂</t>
+          <t>剩的是残值清算</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1656,17 +1648,17 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>39.2</v>
+        <v>41.7</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>42.5</v>
+        <v>44.4</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>应收账款/账期是否被大客户拉长抽</t>
+          <t>把这家五金机械厂的账拆开看</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1704,17 +1696,17 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>42.5</v>
+        <v>44.4</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>44.3</v>
+        <v>47.8</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>③运营视角</t>
+          <t>倒闭极少突发，是现金循环周期被拉长</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1732,11 +1724,7 @@
           <t>【待挑】倒闭关停_仓库_023　搜：empty warehouse / cleared shelves</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：运营视角</t>
-        </is>
-      </c>
+      <c r="I27" s="8" t="inlineStr"/>
       <c r="J27" s="7" t="inlineStr"/>
       <c r="K27" s="7" t="inlineStr">
         <is>
@@ -1756,17 +1744,17 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>44.3</v>
+        <v>47.8</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>47.7</v>
+        <v>49.9</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>成本结构是否失衡（原料涨，终端不涨，增收不增利）</t>
+          <t>应收收不回，存货压钱</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1804,17 +1792,17 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>47.7</v>
+        <v>49.9</v>
       </c>
       <c r="C29" s="7" t="n">
-        <v>49.5</v>
+        <v>52.6</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>④心智视角</t>
+          <t>扩产吞现金，三条管道同时漏</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1832,11 +1820,7 @@
           <t>【待挑】倒闭关停_厂房外景_025　搜：abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
-        <is>
-          <t>视角卡：心智视角</t>
-        </is>
-      </c>
+      <c r="I29" s="8" t="inlineStr"/>
       <c r="J29" s="7" t="inlineStr"/>
       <c r="K29" s="7" t="inlineStr">
         <is>
@@ -1856,17 +1840,17 @@
         </is>
       </c>
       <c r="B30" s="7" t="n">
-        <v>49.5</v>
+        <v>52.6</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>51.3</v>
+        <v>54.7</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>老板是否路径依赖</t>
+          <t>安全垫撑不到回款那天</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1904,17 +1888,17 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>51.3</v>
+        <v>54.7</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>54.4</v>
+        <v>56.6</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>不愿技改升级，把困境归咎大环境</t>
+          <t>看三数，安全垫月数</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -1952,17 +1936,17 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>54.4</v>
+        <v>56.6</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>56.3</v>
+        <v>59.1</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>公开信息点名的问题</t>
+          <t>应收周转天数，资产负债率</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2000,17 +1984,17 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>56.3</v>
+        <v>59.1</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>59.4</v>
+        <v>62.5</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>资产1984万对负债1.21亿</t>
+          <t>（公开数字，1984万，1.21亿</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2056,17 +2040,17 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>59.4</v>
+        <v>62.5</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>62.3</v>
+        <v>65.2</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>两家关联公司实质合并破产清算</t>
+          <t>负债率与现金缺口一目了然）</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2104,10 +2088,10 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>62.3</v>
+        <v>65.2</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>64.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>2.1</v>
@@ -2152,10 +2136,10 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>64.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>66.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>2.5</v>
@@ -2200,17 +2184,17 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>66.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>69.3</v>
+        <v>73.3</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>最后给同类厂三句话</t>
+          <t>记住一句话，潮水退了才知道谁没穿裤</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -2256,17 +2240,17 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>69.3</v>
+        <v>73.3</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>72.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>①留足 6 个月现金安全垫再扩张</t>
+          <t>安全垫比规模重要</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2286,12 +2270,12 @@
       </c>
       <c r="I38" s="8" t="inlineStr">
         <is>
-          <t>数字上大字幕：6 个月</t>
+          <t>避坑清单上屏（≤3 条）</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>数字叮</t>
+          <t>结论咚</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
@@ -2312,17 +2296,17 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>72.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>75.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>②砍掉不赚钱的低端红海单</t>
+          <t>同类厂记住三件事，①留足 6 个月现金安全垫再扩张</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2342,12 +2326,12 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>避坑清单上屏（≤3 条）</t>
+          <t>数字上大字幕：6 个月</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>结论咚</t>
+          <t>数字叮</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
@@ -2368,50 +2352,106 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>75.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>77.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D40" s="7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>②砍掉不赚钱的低端红海单</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>落点/留白</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>实拍+文字卡</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t>【待挑】倒闭关停_货车物流_036　搜：empty loading dock / idle truck</t>
+        </is>
+      </c>
+      <c r="I40" s="8" t="inlineStr">
+        <is>
+          <t>避坑清单上屏（≤3 条）</t>
+        </is>
+      </c>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>结论咚</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>结尾收束</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>叠化</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>037</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>84.8</v>
+      </c>
+      <c r="D41" s="7" t="n">
         <v>2.4</v>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr">
         <is>
           <t>③每年固定比例投技改</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>落点/留白</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
         <is>
           <t>实拍+文字卡</t>
         </is>
       </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_货车物流_036　搜：empty loading dock / idle truck</t>
-        </is>
-      </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>【待挑】倒闭关停_厂房外景_037　搜：abandoned warehouse / factory closed / shutter door</t>
+        </is>
+      </c>
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>避坑清单上屏（≤3 条）</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr">
+      <c r="J41" s="7" t="inlineStr">
         <is>
           <t>结论咚</t>
         </is>
       </c>
-      <c r="K40" s="7" t="inlineStr">
+      <c r="K41" s="7" t="inlineStr">
         <is>
           <t>结尾收束</t>
         </is>
       </c>
-      <c r="L40" s="7" t="inlineStr">
+      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>叠化</t>
         </is>
@@ -2642,7 +2682,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>003、007、011、015、019、023、027、031</t>
+          <t>003、007、011、015、019、023、027、031、035</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -2657,12 +2697,12 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>4-6</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+          <t>本片复用 9 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2768,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>005-006、009-011、029、034</t>
+          <t>002、008-010、013、029、035</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -2771,7 +2811,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>035-036</t>
+          <t>036-037</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">

--- a/workshop/ac3898db99.xlsx
+++ b/workshop/ac3898db99.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：84.8 秒　镜次：37</t>
+          <t>问题类型：倒闭 / 关停　地区：江苏　内容价值：★92.5　总时长：84.8 秒　镜次：36</t>
         </is>
       </c>
     </row>
@@ -803,14 +803,14 @@
         <v>5.7</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>栽在「倒闭 / 关停」上</t>
+          <t>就这么倒下了</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -848,10 +848,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>8.199999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>1.6</v>
@@ -896,10 +896,10 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>13.2</v>
+        <v>11.9</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>3.4</v>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>13.2</v>
+        <v>11.9</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>15.5</v>
+        <v>14.2</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>2.3</v>
@@ -1000,10 +1000,10 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>15.5</v>
+        <v>14.2</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>17.4</v>
+        <v>16.1</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>1.9</v>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>17.4</v>
+        <v>16.1</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>19.3</v>
+        <v>18</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>1.9</v>
@@ -1112,17 +1112,17 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>19.3</v>
+        <v>18</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>21</v>
+        <v>19.7</v>
       </c>
       <c r="D15" s="7" t="n">
         <v>1.7</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>早已停止生产经营</t>
+          <t>公开信息里的数字</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1160,17 +1160,17 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>21</v>
+        <v>19.7</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>22.7</v>
+        <v>22</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>公开信息里的数字</t>
+          <t>1984万，1.21亿</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1188,8 +1188,16 @@
           <t>【待挑】倒闭关停_货车物流_012　搜：empty loading dock / idle truck</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr"/>
-      <c r="J16" s="7" t="inlineStr"/>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>数字上大字幕：1984万，1.21亿</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>数字叮</t>
+        </is>
+      </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -1208,27 +1216,27 @@
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>22.7</v>
+        <v>22</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>25</v>
+        <v>23.8</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>1984万，1.21亿</t>
+          <t>打个比方</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>陈述/数字重音</t>
+          <t>转折/停顿</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>图表+实拍</t>
+          <t>素材(比喻画面)</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
@@ -1236,16 +1244,8 @@
           <t>【待挑】倒闭关停_厂房外景_013　搜：abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t>数字上大字幕：1984万，1.21亿</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>数字叮</t>
-        </is>
-      </c>
+      <c r="I17" s="8" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr"/>
       <c r="K17" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -1264,17 +1264,17 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>25</v>
+        <v>23.8</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>26.8</v>
+        <v>25.6</v>
       </c>
       <c r="D18" s="7" t="n">
         <v>1.8</v>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>打个比方</t>
+          <t>厂子就是一口锅</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1312,17 +1312,17 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>26.8</v>
+        <v>25.6</v>
       </c>
       <c r="C19" s="7" t="n">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>厂子就是一口锅</t>
+          <t>订单是火，现金是锅里的水</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1360,17 +1360,17 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>28.6</v>
+        <v>28.1</v>
       </c>
       <c r="C20" s="7" t="n">
-        <v>31.1</v>
+        <v>30</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>订单是火，现金是锅里的水</t>
+          <t>火一停，水凉得飞快</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1408,27 +1408,27 @@
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>31.1</v>
+        <v>30</v>
       </c>
       <c r="C21" s="7" t="n">
-        <v>33</v>
+        <v>31.9</v>
       </c>
       <c r="D21" s="7" t="n">
         <v>1.9</v>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>火一停，水凉得飞快</t>
+          <t>问题出在哪，一句话</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>逐条拆解</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>图表+文字卡</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
@@ -1456,17 +1456,17 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>33</v>
+        <v>31.9</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>35.1</v>
+        <v>34.2</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>本案的财务病灶很具体</t>
+          <t>几家关联公司捆一起破产</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1504,17 +1504,17 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>35.1</v>
+        <v>34.2</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>37.2</v>
+        <v>36.9</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>关联公司实质合并破产</t>
+          <t>早就不生产了，没人接盘重整</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1552,17 +1552,17 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>37.2</v>
+        <v>36.9</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>39.9</v>
+        <v>38.7</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>早已停止经营，无人申请重整</t>
+          <t>剩点破铜烂铁清算</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1600,17 +1600,17 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>39.9</v>
+        <v>38.7</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>剩的是残值清算</t>
+          <t>把这家五金机械厂的账说人话</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1648,17 +1648,17 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>把这家五金机械厂的账拆开看</t>
+          <t>倒闭很少突然，都是钱慢慢流干</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1696,17 +1696,17 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>44.4</v>
+        <v>44.3</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>47.8</v>
+        <v>46.1</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>倒闭极少突发，是现金循环周期被拉长</t>
+          <t>客户拖着货款不给</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1744,17 +1744,17 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>47.8</v>
+        <v>46.1</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>应收收不回，存货压钱</t>
+          <t>仓库货卖不掉，老板还借钱上新线</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1792,17 +1792,17 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>49.9</v>
+        <v>49.2</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>52.6</v>
       </c>
       <c r="D29" s="7" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>扩产吞现金，三条管道同时漏</t>
+          <t>三条水管一起漏，家底撑不到回款那天就见了底</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1843,14 +1843,14 @@
         <v>52.6</v>
       </c>
       <c r="C30" s="7" t="n">
-        <v>54.7</v>
+        <v>55.7</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>安全垫撑不到回款那天</t>
+          <t>你只盯三个数，兜里钱够花几个月</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1888,17 +1888,17 @@
         </is>
       </c>
       <c r="B31" s="7" t="n">
-        <v>54.7</v>
+        <v>55.7</v>
       </c>
       <c r="C31" s="7" t="n">
-        <v>56.6</v>
+        <v>59</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>看三数，安全垫月数</t>
+          <t>客户拖你多少天，欠的钱是家底几倍</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -1936,17 +1936,17 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>56.6</v>
+        <v>59</v>
       </c>
       <c r="C32" s="7" t="n">
-        <v>59.1</v>
+        <v>62.4</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>应收周转天数，资产负债率</t>
+          <t>（公开数字，1984万，1.21亿</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -1964,8 +1964,16 @@
           <t>【待挑】倒闭关停_货车物流_028　搜：empty loading dock / idle truck</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr"/>
-      <c r="J32" s="7" t="inlineStr"/>
+      <c r="I32" s="8" t="inlineStr">
+        <is>
+          <t>数字上大字幕：1984万，1.21亿</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>数字叮</t>
+        </is>
+      </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -1984,17 +1992,17 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>59.1</v>
+        <v>62.4</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>62.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>（公开数字，1984万，1.21亿</t>
+          <t>负债率与现金缺口一目了然）</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2012,16 +2020,8 @@
           <t>【待挑】倒闭关停_厂房外景_029　搜：abandoned warehouse / factory closed / shutter door</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t>数字上大字幕：1984万，1.21亿</t>
-        </is>
-      </c>
-      <c r="J33" s="7" t="inlineStr">
-        <is>
-          <t>数字叮</t>
-        </is>
-      </c>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr"/>
       <c r="K33" s="7" t="inlineStr">
         <is>
           <t>中段推进</t>
@@ -2040,27 +2040,27 @@
         </is>
       </c>
       <c r="B34" s="7" t="n">
-        <v>62.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="C34" s="7" t="n">
-        <v>65.2</v>
+        <v>67.2</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>负债率与现金缺口一目了然）</t>
+          <t>关门不是哪一天的决定</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>逐条拆解</t>
+          <t>转折/停顿</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>图表+文字卡</t>
+          <t>素材(比喻画面)</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
@@ -2088,17 +2088,17 @@
         </is>
       </c>
       <c r="B35" s="7" t="n">
-        <v>65.2</v>
+        <v>67.2</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>67.3</v>
+        <v>69.7</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>关门不是哪一天的决定</t>
+          <t>是每一次「再撑撑」的累加</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -2136,27 +2136,27 @@
         </is>
       </c>
       <c r="B36" s="7" t="n">
-        <v>67.3</v>
+        <v>69.7</v>
       </c>
       <c r="C36" s="7" t="n">
-        <v>69.8</v>
+        <v>73.2</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>是每一次「再撑撑」的累加</t>
+          <t>记住一句话，潮水退了才知道谁没穿裤</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>转折/停顿</t>
+          <t>落点/留白</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>素材(比喻画面)</t>
+          <t>实拍+文字卡</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
@@ -2164,16 +2164,24 @@
           <t>【待挑】倒闭关停_货车物流_032　搜：empty loading dock / idle truck</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr"/>
-      <c r="J36" s="7" t="inlineStr"/>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>避坑清单上屏（≤3 条）</t>
+        </is>
+      </c>
+      <c r="J36" s="7" t="inlineStr">
+        <is>
+          <t>结论咚</t>
+        </is>
+      </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>中段推进</t>
+          <t>结尾收束</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>硬切</t>
+          <t>叠化</t>
         </is>
       </c>
     </row>
@@ -2184,17 +2192,17 @@
         </is>
       </c>
       <c r="B37" s="7" t="n">
-        <v>69.8</v>
+        <v>73.2</v>
       </c>
       <c r="C37" s="7" t="n">
-        <v>73.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>记住一句话，潮水退了才知道谁没穿裤</t>
+          <t>安全垫比规模重要</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -2240,17 +2248,17 @@
         </is>
       </c>
       <c r="B38" s="7" t="n">
-        <v>73.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="C38" s="7" t="n">
-        <v>75.7</v>
+        <v>79.8</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>安全垫比规模重要</t>
+          <t>同类厂记住三件事，①兜里先留够半年的活钱再扩张</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2296,17 +2304,17 @@
         </is>
       </c>
       <c r="B39" s="7" t="n">
-        <v>75.7</v>
+        <v>79.8</v>
       </c>
       <c r="C39" s="7" t="n">
-        <v>79.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>同类厂记住三件事，①留足 6 个月现金安全垫再扩张</t>
+          <t>②不赚钱的低价单该砍就砍</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2326,12 +2334,12 @@
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>数字上大字幕：6 个月</t>
+          <t>避坑清单上屏（≤3 条）</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>数字叮</t>
+          <t>结论咚</t>
         </is>
       </c>
       <c r="K39" s="7" t="inlineStr">
@@ -2352,17 +2360,17 @@
         </is>
       </c>
       <c r="B40" s="7" t="n">
-        <v>79.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="C40" s="7" t="n">
-        <v>82.40000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="D40" s="7" t="n">
         <v>2.5</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>②砍掉不赚钱的低端红海单</t>
+          <t>③每年匀一笔钱搞技术升级</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -2396,62 +2404,6 @@
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
-        <is>
-          <t>叠化</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>037</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="n">
-        <v>82.40000000000001</v>
-      </c>
-      <c r="C41" s="7" t="n">
-        <v>84.8</v>
-      </c>
-      <c r="D41" s="7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>③每年固定比例投技改</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>落点/留白</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>实拍+文字卡</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t>【待挑】倒闭关停_厂房外景_037　搜：abandoned warehouse / factory closed / shutter door</t>
-        </is>
-      </c>
-      <c r="I41" s="8" t="inlineStr">
-        <is>
-          <t>避坑清单上屏（≤3 条）</t>
-        </is>
-      </c>
-      <c r="J41" s="7" t="inlineStr">
-        <is>
-          <t>结论咚</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>结尾收束</t>
-        </is>
-      </c>
-      <c r="L41" s="7" t="inlineStr">
         <is>
           <t>叠化</t>
         </is>
@@ -2682,7 +2634,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>003、007、011、015、019、023、027、031、035</t>
+          <t>003、007、011、015、019、023、027、031</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
@@ -2697,12 +2649,12 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>4-6</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="I5" s="8" t="inlineStr">
         <is>
-          <t>本片复用 9 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
+          <t>本片复用 8 镜；一次下满，顺着「相似推荐」滚雪球，风格天然统一</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2720,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>002、008-010、013、029、035</t>
+          <t>002、008-010、012、028</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
@@ -2811,7 +2763,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>036-037</t>
+          <t>035-036</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
